--- a/informes/asistencias.xlsx
+++ b/informes/asistencias.xlsx
@@ -267,7 +267,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1634460342" name="Picture">
+        <xdr:cNvPr id="279804191" name="Picture">
 </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
@@ -443,7 +443,7 @@
       <c r="I5" s="5" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">miércoles 27 mayo 2026</t>
+            <t xml:space="preserve">domingo 31 mayo 2026</t>
           </r>
         </is>
       </c>
@@ -610,7 +610,7 @@
       <c r="B11" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Ana Rodríguez Vega</t>
+            <t xml:space="preserve">Javier Sánchez Mora</t>
           </r>
         </is>
       </c>
@@ -619,7 +619,7 @@
       <c r="E11" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32165498E</t>
+            <t xml:space="preserve">11223344F</t>
           </r>
         </is>
       </c>
@@ -628,7 +628,7 @@
       <c r="H11" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">22/5/23, 0:00</t>
+            <t xml:space="preserve">2/03/24 0:00</t>
           </r>
         </is>
       </c>
@@ -638,7 +638,7 @@
       <c r="L11" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1/1/70, 9:20</t>
+            <t xml:space="preserve">1/01/70 7:45</t>
           </r>
         </is>
       </c>
@@ -682,7 +682,7 @@
       <c r="B13" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Ana Rodríguez Vega</t>
+            <t xml:space="preserve">Javier Sánchez Mora</t>
           </r>
         </is>
       </c>
@@ -691,7 +691,7 @@
       <c r="E13" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">32165498E</t>
+            <t xml:space="preserve">11223344F</t>
           </r>
         </is>
       </c>
@@ -700,7 +700,7 @@
       <c r="H13" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">21/5/23, 0:00</t>
+            <t xml:space="preserve">2/03/24 0:00</t>
           </r>
         </is>
       </c>
@@ -710,7 +710,7 @@
       <c r="L13" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1/1/70, 9:10</t>
+            <t xml:space="preserve">1/01/70 7:45</t>
           </r>
         </is>
       </c>
@@ -754,7 +754,7 @@
       <c r="B15" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Laura Martín Santos</t>
+            <t xml:space="preserve">Javier Sánchez Mora</t>
           </r>
         </is>
       </c>
@@ -763,7 +763,7 @@
       <c r="E15" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">78912345D</t>
+            <t xml:space="preserve">11223344F</t>
           </r>
         </is>
       </c>
@@ -772,7 +772,7 @@
       <c r="H15" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">2/4/23, 0:00</t>
+            <t xml:space="preserve">2/03/24 0:00</t>
           </r>
         </is>
       </c>
@@ -782,7 +782,7 @@
       <c r="L15" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1/1/70, 7:30</t>
+            <t xml:space="preserve">1/01/70 7:45</t>
           </r>
         </is>
       </c>
@@ -826,7 +826,7 @@
       <c r="B17" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Luis Fernández Torres</t>
+            <t xml:space="preserve">Diego Castillo </t>
           </r>
         </is>
       </c>
@@ -835,7 +835,7 @@
       <c r="E17" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">45678912C</t>
+            <t xml:space="preserve">99001122H</t>
           </r>
         </is>
       </c>
@@ -844,7 +844,7 @@
       <c r="H17" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">7/3/23, 0:00</t>
+            <t xml:space="preserve">15/02/24 0:00</t>
           </r>
         </is>
       </c>
@@ -854,7 +854,7 @@
       <c r="L17" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1/1/70, 8:45</t>
+            <t xml:space="preserve">1/01/70 10:15</t>
           </r>
         </is>
       </c>
@@ -898,7 +898,7 @@
       <c r="B19" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">María Gómez Ruiz</t>
+            <t xml:space="preserve">Diego Castillo </t>
           </r>
         </is>
       </c>
@@ -907,7 +907,7 @@
       <c r="E19" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">87654321B</t>
+            <t xml:space="preserve">99001122H</t>
           </r>
         </is>
       </c>
@@ -916,7 +916,7 @@
       <c r="H19" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">12/2/23, 0:00</t>
+            <t xml:space="preserve">15/02/24 0:00</t>
           </r>
         </is>
       </c>
@@ -926,7 +926,7 @@
       <c r="L19" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1/1/70, 10:00</t>
+            <t xml:space="preserve">1/01/70 10:15</t>
           </r>
         </is>
       </c>
@@ -970,7 +970,7 @@
       <c r="B21" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Carlos Pérez López</t>
+            <t xml:space="preserve">Diego Castillo </t>
           </r>
         </is>
       </c>
@@ -979,7 +979,7 @@
       <c r="E21" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">12345678A</t>
+            <t xml:space="preserve">99001122H</t>
           </r>
         </is>
       </c>
@@ -988,7 +988,7 @@
       <c r="H21" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">18/1/23, 0:00</t>
+            <t xml:space="preserve">15/02/24 0:00</t>
           </r>
         </is>
       </c>
@@ -998,7 +998,7 @@
       <c r="L21" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1/1/70, 9:15</t>
+            <t xml:space="preserve">1/01/70 10:15</t>
           </r>
         </is>
       </c>
@@ -1042,7 +1042,7 @@
       <c r="B23" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Carlos Pérez López</t>
+            <t xml:space="preserve">Sofía Navarro Gil</t>
           </r>
         </is>
       </c>
@@ -1051,7 +1051,7 @@
       <c r="E23" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">12345678A</t>
+            <t xml:space="preserve">55667788G</t>
           </r>
         </is>
       </c>
@@ -1060,7 +1060,7 @@
       <c r="H23" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">16/1/23, 0:00</t>
+            <t xml:space="preserve">13/01/24 0:00</t>
           </r>
         </is>
       </c>
@@ -1070,7 +1070,7 @@
       <c r="L23" s="8" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">1/1/70, 9:00</t>
+            <t xml:space="preserve">1/01/70 9:00</t>
           </r>
         </is>
       </c>
@@ -1085,7 +1085,7 @@
       <c r="U23" s="1" t="inlineStr"/>
       <c r="V23" s="1" t="inlineStr"/>
     </row>
-    <row r="24" customHeight="1" ht="301">
+    <row r="24" customHeight="1" ht="9">
       <c r="A24" s="1" t="inlineStr"/>
       <c r="B24" s="1" t="inlineStr"/>
       <c r="C24" s="1" t="inlineStr"/>
@@ -1109,55 +1109,55 @@
       <c r="U24" s="1" t="inlineStr"/>
       <c r="V24" s="1" t="inlineStr"/>
     </row>
-    <row r="25" customHeight="1" ht="20">
+    <row r="25" customHeight="1" ht="30">
       <c r="A25" s="1" t="inlineStr"/>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr"/>
-      <c r="D25" s="1" t="inlineStr"/>
-      <c r="E25" s="1" t="inlineStr"/>
-      <c r="F25" s="1" t="inlineStr"/>
-      <c r="G25" s="1" t="inlineStr"/>
-      <c r="H25" s="1" t="inlineStr"/>
-      <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="9" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pagina:</t>
-          </r>
-        </is>
-      </c>
-      <c r="L25" s="9" t="inlineStr"/>
-      <c r="M25" s="9" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">1</t>
-          </r>
-        </is>
-      </c>
-      <c r="N25" s="1" t="inlineStr"/>
-      <c r="O25" s="10" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">/</t>
-          </r>
-        </is>
-      </c>
-      <c r="P25" s="10" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">1</t>
-          </r>
-        </is>
-      </c>
-      <c r="Q25" s="10" t="inlineStr"/>
-      <c r="R25" s="10" t="inlineStr"/>
-      <c r="S25" s="10" t="inlineStr"/>
-      <c r="T25" s="10" t="inlineStr"/>
-      <c r="U25" s="10" t="inlineStr"/>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Sofía Navarro Gil</t>
+          </r>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr"/>
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">55667788G</t>
+          </r>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr"/>
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">13/01/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="inlineStr"/>
+      <c r="K25" s="8" t="inlineStr"/>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 9:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M25" s="8" t="inlineStr"/>
+      <c r="N25" s="8" t="inlineStr"/>
+      <c r="O25" s="8" t="inlineStr"/>
+      <c r="P25" s="8" t="inlineStr"/>
+      <c r="Q25" s="8" t="inlineStr"/>
+      <c r="R25" s="8" t="inlineStr"/>
+      <c r="S25" s="8" t="inlineStr"/>
+      <c r="T25" s="1" t="inlineStr"/>
+      <c r="U25" s="1" t="inlineStr"/>
       <c r="V25" s="1" t="inlineStr"/>
     </row>
-    <row r="26" customHeight="1" ht="10">
+    <row r="26" customHeight="1" ht="9">
       <c r="A26" s="1" t="inlineStr"/>
       <c r="B26" s="1" t="inlineStr"/>
       <c r="C26" s="1" t="inlineStr"/>
@@ -1170,40 +1170,1096 @@
       <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
-      <c r="M26" s="9" t="inlineStr"/>
+      <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr"/>
-      <c r="O26" s="10" t="inlineStr"/>
-      <c r="P26" s="10" t="inlineStr"/>
-      <c r="Q26" s="10" t="inlineStr"/>
-      <c r="R26" s="10" t="inlineStr"/>
-      <c r="S26" s="10" t="inlineStr"/>
-      <c r="T26" s="10" t="inlineStr"/>
-      <c r="U26" s="10" t="inlineStr"/>
+      <c r="O26" s="1" t="inlineStr"/>
+      <c r="P26" s="1" t="inlineStr"/>
+      <c r="Q26" s="1" t="inlineStr"/>
+      <c r="R26" s="1" t="inlineStr"/>
+      <c r="S26" s="1" t="inlineStr"/>
+      <c r="T26" s="1" t="inlineStr"/>
+      <c r="U26" s="1" t="inlineStr"/>
       <c r="V26" s="1" t="inlineStr"/>
     </row>
     <row r="27" customHeight="1" ht="30">
       <c r="A27" s="1" t="inlineStr"/>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr"/>
-      <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
-      <c r="F27" s="1" t="inlineStr"/>
-      <c r="G27" s="1" t="inlineStr"/>
-      <c r="H27" s="1" t="inlineStr"/>
-      <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr"/>
-      <c r="L27" s="1" t="inlineStr"/>
-      <c r="M27" s="1" t="inlineStr"/>
-      <c r="N27" s="1" t="inlineStr"/>
-      <c r="O27" s="1" t="inlineStr"/>
-      <c r="P27" s="1" t="inlineStr"/>
-      <c r="Q27" s="1" t="inlineStr"/>
-      <c r="R27" s="1" t="inlineStr"/>
-      <c r="S27" s="1" t="inlineStr"/>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Sofía Navarro Gil</t>
+          </r>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr"/>
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">55667788G</t>
+          </r>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">13/01/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr"/>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 9:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr"/>
+      <c r="N27" s="8" t="inlineStr"/>
+      <c r="O27" s="8" t="inlineStr"/>
+      <c r="P27" s="8" t="inlineStr"/>
+      <c r="Q27" s="8" t="inlineStr"/>
+      <c r="R27" s="8" t="inlineStr"/>
+      <c r="S27" s="8" t="inlineStr"/>
       <c r="T27" s="1" t="inlineStr"/>
       <c r="U27" s="1" t="inlineStr"/>
       <c r="V27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28" customHeight="1" ht="9">
+      <c r="A28" s="1" t="inlineStr"/>
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr"/>
+      <c r="D28" s="1" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr"/>
+      <c r="F28" s="1" t="inlineStr"/>
+      <c r="G28" s="1" t="inlineStr"/>
+      <c r="H28" s="1" t="inlineStr"/>
+      <c r="I28" s="1" t="inlineStr"/>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
+      <c r="L28" s="1" t="inlineStr"/>
+      <c r="M28" s="1" t="inlineStr"/>
+      <c r="N28" s="1" t="inlineStr"/>
+      <c r="O28" s="1" t="inlineStr"/>
+      <c r="P28" s="1" t="inlineStr"/>
+      <c r="Q28" s="1" t="inlineStr"/>
+      <c r="R28" s="1" t="inlineStr"/>
+      <c r="S28" s="1" t="inlineStr"/>
+      <c r="T28" s="1" t="inlineStr"/>
+      <c r="U28" s="1" t="inlineStr"/>
+      <c r="V28" s="1" t="inlineStr"/>
+    </row>
+    <row r="29" customHeight="1" ht="30">
+      <c r="A29" s="1" t="inlineStr"/>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Javier Sánchez Mora</t>
+          </r>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr"/>
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11223344F</t>
+          </r>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr"/>
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11/01/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr"/>
+      <c r="J29" s="8" t="inlineStr"/>
+      <c r="K29" s="8" t="inlineStr"/>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 8:30</t>
+          </r>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr"/>
+      <c r="N29" s="8" t="inlineStr"/>
+      <c r="O29" s="8" t="inlineStr"/>
+      <c r="P29" s="8" t="inlineStr"/>
+      <c r="Q29" s="8" t="inlineStr"/>
+      <c r="R29" s="8" t="inlineStr"/>
+      <c r="S29" s="8" t="inlineStr"/>
+      <c r="T29" s="1" t="inlineStr"/>
+      <c r="U29" s="1" t="inlineStr"/>
+      <c r="V29" s="1" t="inlineStr"/>
+    </row>
+    <row r="30" customHeight="1" ht="9">
+      <c r="A30" s="1" t="inlineStr"/>
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" s="1" t="inlineStr"/>
+      <c r="D30" s="1" t="inlineStr"/>
+      <c r="E30" s="1" t="inlineStr"/>
+      <c r="F30" s="1" t="inlineStr"/>
+      <c r="G30" s="1" t="inlineStr"/>
+      <c r="H30" s="1" t="inlineStr"/>
+      <c r="I30" s="1" t="inlineStr"/>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
+      <c r="L30" s="1" t="inlineStr"/>
+      <c r="M30" s="1" t="inlineStr"/>
+      <c r="N30" s="1" t="inlineStr"/>
+      <c r="O30" s="1" t="inlineStr"/>
+      <c r="P30" s="1" t="inlineStr"/>
+      <c r="Q30" s="1" t="inlineStr"/>
+      <c r="R30" s="1" t="inlineStr"/>
+      <c r="S30" s="1" t="inlineStr"/>
+      <c r="T30" s="1" t="inlineStr"/>
+      <c r="U30" s="1" t="inlineStr"/>
+      <c r="V30" s="1" t="inlineStr"/>
+    </row>
+    <row r="31" customHeight="1" ht="30">
+      <c r="A31" s="1" t="inlineStr"/>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Javier Sánchez Mora</t>
+          </r>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr"/>
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11223344F</t>
+          </r>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr"/>
+      <c r="G31" s="8" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11/01/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr"/>
+      <c r="J31" s="8" t="inlineStr"/>
+      <c r="K31" s="8" t="inlineStr"/>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 8:30</t>
+          </r>
+        </is>
+      </c>
+      <c r="M31" s="8" t="inlineStr"/>
+      <c r="N31" s="8" t="inlineStr"/>
+      <c r="O31" s="8" t="inlineStr"/>
+      <c r="P31" s="8" t="inlineStr"/>
+      <c r="Q31" s="8" t="inlineStr"/>
+      <c r="R31" s="8" t="inlineStr"/>
+      <c r="S31" s="8" t="inlineStr"/>
+      <c r="T31" s="1" t="inlineStr"/>
+      <c r="U31" s="1" t="inlineStr"/>
+      <c r="V31" s="1" t="inlineStr"/>
+    </row>
+    <row r="32" customHeight="1" ht="9">
+      <c r="A32" s="1" t="inlineStr"/>
+      <c r="B32" s="1" t="inlineStr"/>
+      <c r="C32" s="1" t="inlineStr"/>
+      <c r="D32" s="1" t="inlineStr"/>
+      <c r="E32" s="1" t="inlineStr"/>
+      <c r="F32" s="1" t="inlineStr"/>
+      <c r="G32" s="1" t="inlineStr"/>
+      <c r="H32" s="1" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr"/>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
+      <c r="L32" s="1" t="inlineStr"/>
+      <c r="M32" s="1" t="inlineStr"/>
+      <c r="N32" s="1" t="inlineStr"/>
+      <c r="O32" s="1" t="inlineStr"/>
+      <c r="P32" s="1" t="inlineStr"/>
+      <c r="Q32" s="1" t="inlineStr"/>
+      <c r="R32" s="1" t="inlineStr"/>
+      <c r="S32" s="1" t="inlineStr"/>
+      <c r="T32" s="1" t="inlineStr"/>
+      <c r="U32" s="1" t="inlineStr"/>
+      <c r="V32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33" customHeight="1" ht="30">
+      <c r="A33" s="1" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Javier Sánchez Mora</t>
+          </r>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr"/>
+      <c r="D33" s="8" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11223344F</t>
+          </r>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">11/01/24 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="8" t="inlineStr"/>
+      <c r="K33" s="8" t="inlineStr"/>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 8:30</t>
+          </r>
+        </is>
+      </c>
+      <c r="M33" s="8" t="inlineStr"/>
+      <c r="N33" s="8" t="inlineStr"/>
+      <c r="O33" s="8" t="inlineStr"/>
+      <c r="P33" s="8" t="inlineStr"/>
+      <c r="Q33" s="8" t="inlineStr"/>
+      <c r="R33" s="8" t="inlineStr"/>
+      <c r="S33" s="8" t="inlineStr"/>
+      <c r="T33" s="1" t="inlineStr"/>
+      <c r="U33" s="1" t="inlineStr"/>
+      <c r="V33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34" customHeight="1" ht="9">
+      <c r="A34" s="1" t="inlineStr"/>
+      <c r="B34" s="1" t="inlineStr"/>
+      <c r="C34" s="1" t="inlineStr"/>
+      <c r="D34" s="1" t="inlineStr"/>
+      <c r="E34" s="1" t="inlineStr"/>
+      <c r="F34" s="1" t="inlineStr"/>
+      <c r="G34" s="1" t="inlineStr"/>
+      <c r="H34" s="1" t="inlineStr"/>
+      <c r="I34" s="1" t="inlineStr"/>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
+      <c r="L34" s="1" t="inlineStr"/>
+      <c r="M34" s="1" t="inlineStr"/>
+      <c r="N34" s="1" t="inlineStr"/>
+      <c r="O34" s="1" t="inlineStr"/>
+      <c r="P34" s="1" t="inlineStr"/>
+      <c r="Q34" s="1" t="inlineStr"/>
+      <c r="R34" s="1" t="inlineStr"/>
+      <c r="S34" s="1" t="inlineStr"/>
+      <c r="T34" s="1" t="inlineStr"/>
+      <c r="U34" s="1" t="inlineStr"/>
+      <c r="V34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35" customHeight="1" ht="30">
+      <c r="A35" s="1" t="inlineStr"/>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Ana Rodríguez Vega</t>
+          </r>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr"/>
+      <c r="D35" s="8" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">32165498E</t>
+          </r>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr"/>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">22/05/23 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr"/>
+      <c r="J35" s="8" t="inlineStr"/>
+      <c r="K35" s="8" t="inlineStr"/>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 9:20</t>
+          </r>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr"/>
+      <c r="N35" s="8" t="inlineStr"/>
+      <c r="O35" s="8" t="inlineStr"/>
+      <c r="P35" s="8" t="inlineStr"/>
+      <c r="Q35" s="8" t="inlineStr"/>
+      <c r="R35" s="8" t="inlineStr"/>
+      <c r="S35" s="8" t="inlineStr"/>
+      <c r="T35" s="1" t="inlineStr"/>
+      <c r="U35" s="1" t="inlineStr"/>
+      <c r="V35" s="1" t="inlineStr"/>
+    </row>
+    <row r="36" customHeight="1" ht="67">
+      <c r="A36" s="1" t="inlineStr"/>
+      <c r="B36" s="1" t="inlineStr"/>
+      <c r="C36" s="1" t="inlineStr"/>
+      <c r="D36" s="1" t="inlineStr"/>
+      <c r="E36" s="1" t="inlineStr"/>
+      <c r="F36" s="1" t="inlineStr"/>
+      <c r="G36" s="1" t="inlineStr"/>
+      <c r="H36" s="1" t="inlineStr"/>
+      <c r="I36" s="1" t="inlineStr"/>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
+      <c r="L36" s="1" t="inlineStr"/>
+      <c r="M36" s="1" t="inlineStr"/>
+      <c r="N36" s="1" t="inlineStr"/>
+      <c r="O36" s="1" t="inlineStr"/>
+      <c r="P36" s="1" t="inlineStr"/>
+      <c r="Q36" s="1" t="inlineStr"/>
+      <c r="R36" s="1" t="inlineStr"/>
+      <c r="S36" s="1" t="inlineStr"/>
+      <c r="T36" s="1" t="inlineStr"/>
+      <c r="U36" s="1" t="inlineStr"/>
+      <c r="V36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37" customHeight="1" ht="20">
+      <c r="A37" s="1" t="inlineStr"/>
+      <c r="B37" s="1" t="inlineStr"/>
+      <c r="C37" s="1" t="inlineStr"/>
+      <c r="D37" s="1" t="inlineStr"/>
+      <c r="E37" s="1" t="inlineStr"/>
+      <c r="F37" s="1" t="inlineStr"/>
+      <c r="G37" s="1" t="inlineStr"/>
+      <c r="H37" s="1" t="inlineStr"/>
+      <c r="I37" s="1" t="inlineStr"/>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pagina:</t>
+          </r>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr"/>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1</t>
+          </r>
+        </is>
+      </c>
+      <c r="N37" s="1" t="inlineStr"/>
+      <c r="O37" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">/</t>
+          </r>
+        </is>
+      </c>
+      <c r="P37" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q37" s="10" t="inlineStr"/>
+      <c r="R37" s="10" t="inlineStr"/>
+      <c r="S37" s="10" t="inlineStr"/>
+      <c r="T37" s="10" t="inlineStr"/>
+      <c r="U37" s="10" t="inlineStr"/>
+      <c r="V37" s="1" t="inlineStr"/>
+    </row>
+    <row r="38" customHeight="1" ht="10">
+      <c r="A38" s="1" t="inlineStr"/>
+      <c r="B38" s="1" t="inlineStr"/>
+      <c r="C38" s="1" t="inlineStr"/>
+      <c r="D38" s="1" t="inlineStr"/>
+      <c r="E38" s="1" t="inlineStr"/>
+      <c r="F38" s="1" t="inlineStr"/>
+      <c r="G38" s="1" t="inlineStr"/>
+      <c r="H38" s="1" t="inlineStr"/>
+      <c r="I38" s="1" t="inlineStr"/>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
+      <c r="L38" s="1" t="inlineStr"/>
+      <c r="M38" s="9" t="inlineStr"/>
+      <c r="N38" s="1" t="inlineStr"/>
+      <c r="O38" s="10" t="inlineStr"/>
+      <c r="P38" s="10" t="inlineStr"/>
+      <c r="Q38" s="10" t="inlineStr"/>
+      <c r="R38" s="10" t="inlineStr"/>
+      <c r="S38" s="10" t="inlineStr"/>
+      <c r="T38" s="10" t="inlineStr"/>
+      <c r="U38" s="10" t="inlineStr"/>
+      <c r="V38" s="1" t="inlineStr"/>
+    </row>
+    <row r="39" customHeight="1" ht="30">
+      <c r="A39" s="1" t="inlineStr"/>
+      <c r="B39" s="1" t="inlineStr"/>
+      <c r="C39" s="1" t="inlineStr"/>
+      <c r="D39" s="1" t="inlineStr"/>
+      <c r="E39" s="1" t="inlineStr"/>
+      <c r="F39" s="1" t="inlineStr"/>
+      <c r="G39" s="1" t="inlineStr"/>
+      <c r="H39" s="1" t="inlineStr"/>
+      <c r="I39" s="1" t="inlineStr"/>
+      <c r="J39" s="1" t="inlineStr"/>
+      <c r="K39" s="1" t="inlineStr"/>
+      <c r="L39" s="1" t="inlineStr"/>
+      <c r="M39" s="1" t="inlineStr"/>
+      <c r="N39" s="1" t="inlineStr"/>
+      <c r="O39" s="1" t="inlineStr"/>
+      <c r="P39" s="1" t="inlineStr"/>
+      <c r="Q39" s="1" t="inlineStr"/>
+      <c r="R39" s="1" t="inlineStr"/>
+      <c r="S39" s="1" t="inlineStr"/>
+      <c r="T39" s="1" t="inlineStr"/>
+      <c r="U39" s="1" t="inlineStr"/>
+      <c r="V39" s="1" t="inlineStr"/>
+    </row>
+    <row r="40" customHeight="1" ht="20">
+      <c r="A40" s="1" t="inlineStr"/>
+      <c r="B40" s="1" t="inlineStr"/>
+      <c r="C40" s="1" t="inlineStr"/>
+      <c r="D40" s="1" t="inlineStr"/>
+      <c r="E40" s="1" t="inlineStr"/>
+      <c r="F40" s="1" t="inlineStr"/>
+      <c r="G40" s="1" t="inlineStr"/>
+      <c r="H40" s="1" t="inlineStr"/>
+      <c r="I40" s="1" t="inlineStr"/>
+      <c r="J40" s="1" t="inlineStr"/>
+      <c r="K40" s="1" t="inlineStr"/>
+      <c r="L40" s="1" t="inlineStr"/>
+      <c r="M40" s="1" t="inlineStr"/>
+      <c r="N40" s="1" t="inlineStr"/>
+      <c r="O40" s="1" t="inlineStr"/>
+      <c r="P40" s="1" t="inlineStr"/>
+      <c r="Q40" s="1" t="inlineStr"/>
+      <c r="R40" s="1" t="inlineStr"/>
+      <c r="S40" s="1" t="inlineStr"/>
+      <c r="T40" s="1" t="inlineStr"/>
+      <c r="U40" s="1" t="inlineStr"/>
+      <c r="V40" s="1" t="inlineStr"/>
+    </row>
+    <row r="41" customHeight="1" ht="30">
+      <c r="A41" s="1" t="inlineStr"/>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Socio</t>
+          </r>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">DNI</t>
+          </r>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Fecha Asistencia</t>
+          </r>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Hora entrada</t>
+          </r>
+        </is>
+      </c>
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+      <c r="O41" s="7" t="inlineStr"/>
+      <c r="P41" s="7" t="inlineStr"/>
+      <c r="Q41" s="7" t="inlineStr"/>
+      <c r="R41" s="7" t="inlineStr"/>
+      <c r="S41" s="1" t="inlineStr"/>
+      <c r="T41" s="1" t="inlineStr"/>
+      <c r="U41" s="1" t="inlineStr"/>
+      <c r="V41" s="1" t="inlineStr"/>
+    </row>
+    <row r="42" customHeight="1" ht="10">
+      <c r="A42" s="1" t="inlineStr"/>
+      <c r="B42" s="1" t="inlineStr"/>
+      <c r="C42" s="1" t="inlineStr"/>
+      <c r="D42" s="1" t="inlineStr"/>
+      <c r="E42" s="1" t="inlineStr"/>
+      <c r="F42" s="1" t="inlineStr"/>
+      <c r="G42" s="1" t="inlineStr"/>
+      <c r="H42" s="1" t="inlineStr"/>
+      <c r="I42" s="1" t="inlineStr"/>
+      <c r="J42" s="1" t="inlineStr"/>
+      <c r="K42" s="1" t="inlineStr"/>
+      <c r="L42" s="1" t="inlineStr"/>
+      <c r="M42" s="1" t="inlineStr"/>
+      <c r="N42" s="1" t="inlineStr"/>
+      <c r="O42" s="1" t="inlineStr"/>
+      <c r="P42" s="1" t="inlineStr"/>
+      <c r="Q42" s="1" t="inlineStr"/>
+      <c r="R42" s="1" t="inlineStr"/>
+      <c r="S42" s="1" t="inlineStr"/>
+      <c r="T42" s="1" t="inlineStr"/>
+      <c r="U42" s="1" t="inlineStr"/>
+      <c r="V42" s="1" t="inlineStr"/>
+    </row>
+    <row r="43" customHeight="1" ht="30">
+      <c r="A43" s="1" t="inlineStr"/>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Ana Rodríguez Vega</t>
+          </r>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr"/>
+      <c r="D43" s="8" t="inlineStr"/>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">32165498E</t>
+          </r>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr"/>
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">21/05/23 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr"/>
+      <c r="J43" s="8" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 9:10</t>
+          </r>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr"/>
+      <c r="N43" s="8" t="inlineStr"/>
+      <c r="O43" s="8" t="inlineStr"/>
+      <c r="P43" s="8" t="inlineStr"/>
+      <c r="Q43" s="8" t="inlineStr"/>
+      <c r="R43" s="8" t="inlineStr"/>
+      <c r="S43" s="8" t="inlineStr"/>
+      <c r="T43" s="1" t="inlineStr"/>
+      <c r="U43" s="1" t="inlineStr"/>
+      <c r="V43" s="1" t="inlineStr"/>
+    </row>
+    <row r="44" customHeight="1" ht="9">
+      <c r="A44" s="1" t="inlineStr"/>
+      <c r="B44" s="1" t="inlineStr"/>
+      <c r="C44" s="1" t="inlineStr"/>
+      <c r="D44" s="1" t="inlineStr"/>
+      <c r="E44" s="1" t="inlineStr"/>
+      <c r="F44" s="1" t="inlineStr"/>
+      <c r="G44" s="1" t="inlineStr"/>
+      <c r="H44" s="1" t="inlineStr"/>
+      <c r="I44" s="1" t="inlineStr"/>
+      <c r="J44" s="1" t="inlineStr"/>
+      <c r="K44" s="1" t="inlineStr"/>
+      <c r="L44" s="1" t="inlineStr"/>
+      <c r="M44" s="1" t="inlineStr"/>
+      <c r="N44" s="1" t="inlineStr"/>
+      <c r="O44" s="1" t="inlineStr"/>
+      <c r="P44" s="1" t="inlineStr"/>
+      <c r="Q44" s="1" t="inlineStr"/>
+      <c r="R44" s="1" t="inlineStr"/>
+      <c r="S44" s="1" t="inlineStr"/>
+      <c r="T44" s="1" t="inlineStr"/>
+      <c r="U44" s="1" t="inlineStr"/>
+      <c r="V44" s="1" t="inlineStr"/>
+    </row>
+    <row r="45" customHeight="1" ht="30">
+      <c r="A45" s="1" t="inlineStr"/>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Laura Martín Santos</t>
+          </r>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr"/>
+      <c r="D45" s="8" t="inlineStr"/>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">78912345D</t>
+          </r>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2/04/23 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr"/>
+      <c r="J45" s="8" t="inlineStr"/>
+      <c r="K45" s="8" t="inlineStr"/>
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 7:30</t>
+          </r>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr"/>
+      <c r="N45" s="8" t="inlineStr"/>
+      <c r="O45" s="8" t="inlineStr"/>
+      <c r="P45" s="8" t="inlineStr"/>
+      <c r="Q45" s="8" t="inlineStr"/>
+      <c r="R45" s="8" t="inlineStr"/>
+      <c r="S45" s="8" t="inlineStr"/>
+      <c r="T45" s="1" t="inlineStr"/>
+      <c r="U45" s="1" t="inlineStr"/>
+      <c r="V45" s="1" t="inlineStr"/>
+    </row>
+    <row r="46" customHeight="1" ht="9">
+      <c r="A46" s="1" t="inlineStr"/>
+      <c r="B46" s="1" t="inlineStr"/>
+      <c r="C46" s="1" t="inlineStr"/>
+      <c r="D46" s="1" t="inlineStr"/>
+      <c r="E46" s="1" t="inlineStr"/>
+      <c r="F46" s="1" t="inlineStr"/>
+      <c r="G46" s="1" t="inlineStr"/>
+      <c r="H46" s="1" t="inlineStr"/>
+      <c r="I46" s="1" t="inlineStr"/>
+      <c r="J46" s="1" t="inlineStr"/>
+      <c r="K46" s="1" t="inlineStr"/>
+      <c r="L46" s="1" t="inlineStr"/>
+      <c r="M46" s="1" t="inlineStr"/>
+      <c r="N46" s="1" t="inlineStr"/>
+      <c r="O46" s="1" t="inlineStr"/>
+      <c r="P46" s="1" t="inlineStr"/>
+      <c r="Q46" s="1" t="inlineStr"/>
+      <c r="R46" s="1" t="inlineStr"/>
+      <c r="S46" s="1" t="inlineStr"/>
+      <c r="T46" s="1" t="inlineStr"/>
+      <c r="U46" s="1" t="inlineStr"/>
+      <c r="V46" s="1" t="inlineStr"/>
+    </row>
+    <row r="47" customHeight="1" ht="30">
+      <c r="A47" s="1" t="inlineStr"/>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Luis Fernández Torres</t>
+          </r>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr"/>
+      <c r="D47" s="8" t="inlineStr"/>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">45678912C</t>
+          </r>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr"/>
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">7/03/23 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I47" s="8" t="inlineStr"/>
+      <c r="J47" s="8" t="inlineStr"/>
+      <c r="K47" s="8" t="inlineStr"/>
+      <c r="L47" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 8:45</t>
+          </r>
+        </is>
+      </c>
+      <c r="M47" s="8" t="inlineStr"/>
+      <c r="N47" s="8" t="inlineStr"/>
+      <c r="O47" s="8" t="inlineStr"/>
+      <c r="P47" s="8" t="inlineStr"/>
+      <c r="Q47" s="8" t="inlineStr"/>
+      <c r="R47" s="8" t="inlineStr"/>
+      <c r="S47" s="8" t="inlineStr"/>
+      <c r="T47" s="1" t="inlineStr"/>
+      <c r="U47" s="1" t="inlineStr"/>
+      <c r="V47" s="1" t="inlineStr"/>
+    </row>
+    <row r="48" customHeight="1" ht="9">
+      <c r="A48" s="1" t="inlineStr"/>
+      <c r="B48" s="1" t="inlineStr"/>
+      <c r="C48" s="1" t="inlineStr"/>
+      <c r="D48" s="1" t="inlineStr"/>
+      <c r="E48" s="1" t="inlineStr"/>
+      <c r="F48" s="1" t="inlineStr"/>
+      <c r="G48" s="1" t="inlineStr"/>
+      <c r="H48" s="1" t="inlineStr"/>
+      <c r="I48" s="1" t="inlineStr"/>
+      <c r="J48" s="1" t="inlineStr"/>
+      <c r="K48" s="1" t="inlineStr"/>
+      <c r="L48" s="1" t="inlineStr"/>
+      <c r="M48" s="1" t="inlineStr"/>
+      <c r="N48" s="1" t="inlineStr"/>
+      <c r="O48" s="1" t="inlineStr"/>
+      <c r="P48" s="1" t="inlineStr"/>
+      <c r="Q48" s="1" t="inlineStr"/>
+      <c r="R48" s="1" t="inlineStr"/>
+      <c r="S48" s="1" t="inlineStr"/>
+      <c r="T48" s="1" t="inlineStr"/>
+      <c r="U48" s="1" t="inlineStr"/>
+      <c r="V48" s="1" t="inlineStr"/>
+    </row>
+    <row r="49" customHeight="1" ht="30">
+      <c r="A49" s="1" t="inlineStr"/>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">María Gómez Ruiz</t>
+          </r>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr"/>
+      <c r="D49" s="8" t="inlineStr"/>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">87654321B</t>
+          </r>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr"/>
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">12/02/23 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I49" s="8" t="inlineStr"/>
+      <c r="J49" s="8" t="inlineStr"/>
+      <c r="K49" s="8" t="inlineStr"/>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 10:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M49" s="8" t="inlineStr"/>
+      <c r="N49" s="8" t="inlineStr"/>
+      <c r="O49" s="8" t="inlineStr"/>
+      <c r="P49" s="8" t="inlineStr"/>
+      <c r="Q49" s="8" t="inlineStr"/>
+      <c r="R49" s="8" t="inlineStr"/>
+      <c r="S49" s="8" t="inlineStr"/>
+      <c r="T49" s="1" t="inlineStr"/>
+      <c r="U49" s="1" t="inlineStr"/>
+      <c r="V49" s="1" t="inlineStr"/>
+    </row>
+    <row r="50" customHeight="1" ht="9">
+      <c r="A50" s="1" t="inlineStr"/>
+      <c r="B50" s="1" t="inlineStr"/>
+      <c r="C50" s="1" t="inlineStr"/>
+      <c r="D50" s="1" t="inlineStr"/>
+      <c r="E50" s="1" t="inlineStr"/>
+      <c r="F50" s="1" t="inlineStr"/>
+      <c r="G50" s="1" t="inlineStr"/>
+      <c r="H50" s="1" t="inlineStr"/>
+      <c r="I50" s="1" t="inlineStr"/>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
+      <c r="L50" s="1" t="inlineStr"/>
+      <c r="M50" s="1" t="inlineStr"/>
+      <c r="N50" s="1" t="inlineStr"/>
+      <c r="O50" s="1" t="inlineStr"/>
+      <c r="P50" s="1" t="inlineStr"/>
+      <c r="Q50" s="1" t="inlineStr"/>
+      <c r="R50" s="1" t="inlineStr"/>
+      <c r="S50" s="1" t="inlineStr"/>
+      <c r="T50" s="1" t="inlineStr"/>
+      <c r="U50" s="1" t="inlineStr"/>
+      <c r="V50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51" customHeight="1" ht="30">
+      <c r="A51" s="1" t="inlineStr"/>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Carlos Pérez López</t>
+          </r>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr"/>
+      <c r="D51" s="8" t="inlineStr"/>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">12345678A</t>
+          </r>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr"/>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">18/01/23 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr"/>
+      <c r="J51" s="8" t="inlineStr"/>
+      <c r="K51" s="8" t="inlineStr"/>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 9:15</t>
+          </r>
+        </is>
+      </c>
+      <c r="M51" s="8" t="inlineStr"/>
+      <c r="N51" s="8" t="inlineStr"/>
+      <c r="O51" s="8" t="inlineStr"/>
+      <c r="P51" s="8" t="inlineStr"/>
+      <c r="Q51" s="8" t="inlineStr"/>
+      <c r="R51" s="8" t="inlineStr"/>
+      <c r="S51" s="8" t="inlineStr"/>
+      <c r="T51" s="1" t="inlineStr"/>
+      <c r="U51" s="1" t="inlineStr"/>
+      <c r="V51" s="1" t="inlineStr"/>
+    </row>
+    <row r="52" customHeight="1" ht="9">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="inlineStr"/>
+      <c r="M52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr"/>
+      <c r="O52" s="1" t="inlineStr"/>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr"/>
+      <c r="V52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53" customHeight="1" ht="30">
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Carlos Pérez López</t>
+          </r>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr"/>
+      <c r="D53" s="8" t="inlineStr"/>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">12345678A</t>
+          </r>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr"/>
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">16/01/23 0:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="I53" s="8" t="inlineStr"/>
+      <c r="J53" s="8" t="inlineStr"/>
+      <c r="K53" s="8" t="inlineStr"/>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">1/01/70 9:00</t>
+          </r>
+        </is>
+      </c>
+      <c r="M53" s="8" t="inlineStr"/>
+      <c r="N53" s="8" t="inlineStr"/>
+      <c r="O53" s="8" t="inlineStr"/>
+      <c r="P53" s="8" t="inlineStr"/>
+      <c r="Q53" s="8" t="inlineStr"/>
+      <c r="R53" s="8" t="inlineStr"/>
+      <c r="S53" s="8" t="inlineStr"/>
+      <c r="T53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="inlineStr"/>
+      <c r="V53" s="1" t="inlineStr"/>
+    </row>
+    <row r="54" customHeight="1" ht="497">
+      <c r="A54" s="1" t="inlineStr"/>
+      <c r="B54" s="1" t="inlineStr"/>
+      <c r="C54" s="1" t="inlineStr"/>
+      <c r="D54" s="1" t="inlineStr"/>
+      <c r="E54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr"/>
+      <c r="G54" s="1" t="inlineStr"/>
+      <c r="H54" s="1" t="inlineStr"/>
+      <c r="I54" s="1" t="inlineStr"/>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
+      <c r="L54" s="1" t="inlineStr"/>
+      <c r="M54" s="1" t="inlineStr"/>
+      <c r="N54" s="1" t="inlineStr"/>
+      <c r="O54" s="1" t="inlineStr"/>
+      <c r="P54" s="1" t="inlineStr"/>
+      <c r="Q54" s="1" t="inlineStr"/>
+      <c r="R54" s="1" t="inlineStr"/>
+      <c r="S54" s="1" t="inlineStr"/>
+      <c r="T54" s="1" t="inlineStr"/>
+      <c r="U54" s="1" t="inlineStr"/>
+      <c r="V54" s="1" t="inlineStr"/>
+    </row>
+    <row r="55" customHeight="1" ht="20">
+      <c r="A55" s="1" t="inlineStr"/>
+      <c r="B55" s="1" t="inlineStr"/>
+      <c r="C55" s="1" t="inlineStr"/>
+      <c r="D55" s="1" t="inlineStr"/>
+      <c r="E55" s="1" t="inlineStr"/>
+      <c r="F55" s="1" t="inlineStr"/>
+      <c r="G55" s="1" t="inlineStr"/>
+      <c r="H55" s="1" t="inlineStr"/>
+      <c r="I55" s="1" t="inlineStr"/>
+      <c r="J55" s="1" t="inlineStr"/>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">Pagina:</t>
+          </r>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr"/>
+      <c r="M55" s="9" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2</t>
+          </r>
+        </is>
+      </c>
+      <c r="N55" s="1" t="inlineStr"/>
+      <c r="O55" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">/</t>
+          </r>
+        </is>
+      </c>
+      <c r="P55" s="10" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">2</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q55" s="10" t="inlineStr"/>
+      <c r="R55" s="10" t="inlineStr"/>
+      <c r="S55" s="10" t="inlineStr"/>
+      <c r="T55" s="10" t="inlineStr"/>
+      <c r="U55" s="10" t="inlineStr"/>
+      <c r="V55" s="1" t="inlineStr"/>
+    </row>
+    <row r="56" customHeight="1" ht="10">
+      <c r="A56" s="1" t="inlineStr"/>
+      <c r="B56" s="1" t="inlineStr"/>
+      <c r="C56" s="1" t="inlineStr"/>
+      <c r="D56" s="1" t="inlineStr"/>
+      <c r="E56" s="1" t="inlineStr"/>
+      <c r="F56" s="1" t="inlineStr"/>
+      <c r="G56" s="1" t="inlineStr"/>
+      <c r="H56" s="1" t="inlineStr"/>
+      <c r="I56" s="1" t="inlineStr"/>
+      <c r="J56" s="1" t="inlineStr"/>
+      <c r="K56" s="1" t="inlineStr"/>
+      <c r="L56" s="1" t="inlineStr"/>
+      <c r="M56" s="9" t="inlineStr"/>
+      <c r="N56" s="1" t="inlineStr"/>
+      <c r="O56" s="10" t="inlineStr"/>
+      <c r="P56" s="10" t="inlineStr"/>
+      <c r="Q56" s="10" t="inlineStr"/>
+      <c r="R56" s="10" t="inlineStr"/>
+      <c r="S56" s="10" t="inlineStr"/>
+      <c r="T56" s="10" t="inlineStr"/>
+      <c r="U56" s="10" t="inlineStr"/>
+      <c r="V56" s="1" t="inlineStr"/>
+    </row>
+    <row r="57" customHeight="1" ht="30">
+      <c r="A57" s="1" t="inlineStr"/>
+      <c r="B57" s="1" t="inlineStr"/>
+      <c r="C57" s="1" t="inlineStr"/>
+      <c r="D57" s="1" t="inlineStr"/>
+      <c r="E57" s="1" t="inlineStr"/>
+      <c r="F57" s="1" t="inlineStr"/>
+      <c r="G57" s="1" t="inlineStr"/>
+      <c r="H57" s="1" t="inlineStr"/>
+      <c r="I57" s="1" t="inlineStr"/>
+      <c r="J57" s="1" t="inlineStr"/>
+      <c r="K57" s="1" t="inlineStr"/>
+      <c r="L57" s="1" t="inlineStr"/>
+      <c r="M57" s="1" t="inlineStr"/>
+      <c r="N57" s="1" t="inlineStr"/>
+      <c r="O57" s="1" t="inlineStr"/>
+      <c r="P57" s="1" t="inlineStr"/>
+      <c r="Q57" s="1" t="inlineStr"/>
+      <c r="R57" s="1" t="inlineStr"/>
+      <c r="S57" s="1" t="inlineStr"/>
+      <c r="T57" s="1" t="inlineStr"/>
+      <c r="U57" s="1" t="inlineStr"/>
+      <c r="V57" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -1244,10 +2300,66 @@
     <mergeCell ref="E23:G23"/>
     <mergeCell ref="H23:K23"/>
     <mergeCell ref="L23:S23"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:U26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="H25:K25"/>
+    <mergeCell ref="L25:S25"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="H27:K27"/>
+    <mergeCell ref="L27:S27"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="H29:K29"/>
+    <mergeCell ref="L29:S29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="L31:S31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="L33:S33"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="L35:S35"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:M38"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="P37:U38"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="L41:R41"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="H43:K43"/>
+    <mergeCell ref="L43:S43"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="L45:S45"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="L47:S47"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="H49:K49"/>
+    <mergeCell ref="L49:S49"/>
+    <mergeCell ref="B51:D51"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="H51:K51"/>
+    <mergeCell ref="L51:S51"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="E53:G53"/>
+    <mergeCell ref="H53:K53"/>
+    <mergeCell ref="L53:S53"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="M55:M56"/>
+    <mergeCell ref="O55:O56"/>
+    <mergeCell ref="P55:U56"/>
   </mergeCells>
   <pageMargins left="0.0" right="0.0" top="0.0" bottom="0.00" header="0.0" footer="0.0"/>
   <pageSetup orientation="portrait" paperSize="9"/>
